--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a1.00_b1.00_x0.01_Q80_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a1.00_b1.00_x0.01_Q80_LO.xlsx
@@ -455,10 +455,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0006322448965476169</v>
+        <v>0.0002860294061164332</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0006322448965476169</v>
+        <v>0.0002860294061164332</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -469,10 +469,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0009908068383842864</v>
+        <v>0.0004579750754086259</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0009908068383842864</v>
+        <v>0.0004579750754086259</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -483,10 +483,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.001883207785607583</v>
+        <v>0.0008706508298524689</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001883207785607583</v>
+        <v>0.0008706508298524689</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -497,10 +497,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.003015265348318728</v>
+        <v>0.001391633792766105</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003015265348318728</v>
+        <v>0.001391633792766105</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -511,10 +511,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.003915845539456046</v>
+        <v>0.001810954448418933</v>
       </c>
       <c r="C6" t="n">
-        <v>0.003915845539456046</v>
+        <v>0.001810954448418933</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -525,10 +525,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.004181957476579958</v>
+        <v>0.001932741188127607</v>
       </c>
       <c r="C7" t="n">
-        <v>0.004181957476579958</v>
+        <v>0.001932741188127607</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -539,10 +539,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.004039250517273229</v>
+        <v>0.001866119805847679</v>
       </c>
       <c r="C8" t="n">
-        <v>0.004039250517273229</v>
+        <v>0.001866119805847679</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -553,10 +553,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.003765175815982103</v>
+        <v>0.001740467224702925</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003765175815982103</v>
+        <v>0.001740467224702925</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -567,10 +567,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.003488355193537002</v>
+        <v>0.00161135970239504</v>
       </c>
       <c r="C10" t="n">
-        <v>0.003488355193537002</v>
+        <v>0.00161135970239504</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -581,10 +581,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.003325212284299242</v>
+        <v>0.001493602238812451</v>
       </c>
       <c r="C11" t="n">
-        <v>0.003325212284299242</v>
+        <v>0.001493602238812451</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
